--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.4273954014621</v>
+        <v>9.331951752737591</v>
       </c>
       <c r="D2" t="n">
-        <v>30.80584360149873</v>
+        <v>5.005949585243543</v>
       </c>
       <c r="E2" t="n">
-        <v>13.09242681679972</v>
+        <v>2.127519357729954</v>
       </c>
       <c r="F2" t="n">
-        <v>10.76862125068006</v>
+        <v>1.74990095323551</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.59146738069023</v>
+        <v>6.108613449362163</v>
       </c>
       <c r="D3" t="n">
-        <v>8.06066848451376</v>
+        <v>1.309858628733486</v>
       </c>
       <c r="E3" t="n">
-        <v>13.09242681679972</v>
+        <v>2.127519357729954</v>
       </c>
       <c r="F3" t="n">
-        <v>10.76862125068006</v>
+        <v>1.74990095323551</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.90342391499762</v>
+        <v>4.859306386187114</v>
       </c>
       <c r="D4" t="n">
-        <v>30.01039657528128</v>
+        <v>4.876689443483208</v>
       </c>
       <c r="E4" t="n">
-        <v>13.09242681679972</v>
+        <v>2.127519357729954</v>
       </c>
       <c r="F4" t="n">
-        <v>10.76862125068006</v>
+        <v>1.74990095323551</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.35203779528628</v>
+        <v>3.79470614173402</v>
       </c>
       <c r="D5" t="n">
-        <v>23.79911108041282</v>
+        <v>3.867355550567083</v>
       </c>
       <c r="E5" t="n">
-        <v>13.09242681679972</v>
+        <v>2.127519357729954</v>
       </c>
       <c r="F5" t="n">
-        <v>10.76862125068006</v>
+        <v>1.74990095323551</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>11.42459720548023</v>
+        <v>1.856497045890537</v>
       </c>
       <c r="D6" t="n">
-        <v>10.85634579266485</v>
+        <v>1.764156191308037</v>
       </c>
       <c r="E6" t="n">
-        <v>13.09242681679972</v>
+        <v>2.127519357729954</v>
       </c>
       <c r="F6" t="n">
-        <v>10.76862125068006</v>
+        <v>1.74990095323551</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.27578026080057</v>
+        <v>6.382314292380094</v>
       </c>
       <c r="D7" t="n">
-        <v>38.94868418830089</v>
+        <v>6.329161180598896</v>
       </c>
       <c r="E7" t="n">
-        <v>13.09242681679972</v>
+        <v>2.127519357729954</v>
       </c>
       <c r="F7" t="n">
-        <v>10.76862125068006</v>
+        <v>1.74990095323551</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.10555800223317</v>
+        <v>6.19215317536289</v>
       </c>
       <c r="D8" t="n">
-        <v>38.02996698110178</v>
+        <v>6.179869634429039</v>
       </c>
       <c r="E8" t="n">
-        <v>13.09242681679972</v>
+        <v>2.127519357729954</v>
       </c>
       <c r="F8" t="n">
-        <v>10.76862125068006</v>
+        <v>1.74990095323551</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.69401483710639</v>
+        <v>2.875277411029789</v>
       </c>
       <c r="D9" t="n">
-        <v>18.06616976542736</v>
+        <v>2.935752586881946</v>
       </c>
       <c r="E9" t="n">
-        <v>13.09242681679972</v>
+        <v>2.127519357729954</v>
       </c>
       <c r="F9" t="n">
-        <v>10.76862125068006</v>
+        <v>1.74990095323551</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.81654840637311</v>
+        <v>3.707689116035631</v>
       </c>
       <c r="D10" t="n">
-        <v>22.79511217546323</v>
+        <v>3.704205728512775</v>
       </c>
       <c r="E10" t="n">
-        <v>13.09242681679972</v>
+        <v>2.127519357729954</v>
       </c>
       <c r="F10" t="n">
-        <v>10.76862125068006</v>
+        <v>1.74990095323551</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.26200648853601</v>
+        <v>4.430076054387101</v>
       </c>
       <c r="D11" t="n">
-        <v>26.829975881949</v>
+        <v>4.359871080816712</v>
       </c>
       <c r="E11" t="n">
-        <v>13.09242681679972</v>
+        <v>2.127519357729954</v>
       </c>
       <c r="F11" t="n">
-        <v>10.76862125068006</v>
+        <v>1.74990095323551</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>13.90707293449248</v>
+        <v>2.259899351855028</v>
       </c>
       <c r="D12" t="n">
-        <v>13.45952253750289</v>
+        <v>2.187172412344219</v>
       </c>
       <c r="E12" t="n">
-        <v>13.09242681679972</v>
+        <v>2.127519357729954</v>
       </c>
       <c r="F12" t="n">
-        <v>10.76862125068006</v>
+        <v>1.74990095323551</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>7.286348416821739</v>
+        <v>1.184031617733533</v>
       </c>
       <c r="D13" t="n">
-        <v>7.966137718037816</v>
+        <v>1.294497379181145</v>
       </c>
       <c r="E13" t="n">
-        <v>13.09242681679972</v>
+        <v>2.127519357729954</v>
       </c>
       <c r="F13" t="n">
-        <v>10.76862125068006</v>
+        <v>1.74990095323551</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>42.69357260572744</v>
+        <v>6.937705548430709</v>
       </c>
       <c r="D14" t="n">
-        <v>41.92508263026991</v>
+        <v>6.81282592741886</v>
       </c>
       <c r="E14" t="n">
-        <v>13.09242681679972</v>
+        <v>2.127519357729954</v>
       </c>
       <c r="F14" t="n">
-        <v>10.76862125068006</v>
+        <v>1.74990095323551</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>17.83312956127126</v>
+        <v>2.897883553706579</v>
       </c>
       <c r="D15" t="n">
-        <v>17.19834870455851</v>
+        <v>2.794731664490758</v>
       </c>
       <c r="E15" t="n">
-        <v>13.09242681679972</v>
+        <v>2.127519357729954</v>
       </c>
       <c r="F15" t="n">
-        <v>10.76862125068006</v>
+        <v>1.74990095323551</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>30.04340956837373</v>
+        <v>4.882054054860732</v>
       </c>
       <c r="D16" t="n">
-        <v>29.44345384097034</v>
+        <v>4.78456124915768</v>
       </c>
       <c r="E16" t="n">
-        <v>13.09242681679972</v>
+        <v>2.127519357729954</v>
       </c>
       <c r="F16" t="n">
-        <v>10.76862125068006</v>
+        <v>1.74990095323551</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
